--- a/config/excel/CfgCombatSkills.xlsx
+++ b/config/excel/CfgCombatSkills.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatSkills" sheetId="1" r:id="R0d68b889bc334cfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatSkills" sheetId="1" r:id="Rde11d8c89507431a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,6 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.###"/>
+    <x:numFmt numFmtId="202" formatCode="General"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -29,7 +34,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -44,6 +49,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -58,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -80,6 +115,39 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -285,111 +353,179 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17.600000381469727" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>DurationTicks</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>CooldownTicks</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>StartRange</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>StartRangeSource</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="17" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="17" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="17" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" s="17" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
+      <x:c r="E2" s="17" t="str">
         <x:v>int</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="18" t="str">
         <x:v># 战斗技能编号。</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="18" t="str">
         <x:v>一次施法持续逻辑帧。</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="18" t="str">
         <x:v>施法后冷却逻辑帧。</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="18" t="str">
         <x:v>固定起手距离或装备攻击范围附加值。</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str">
+      <x:c r="E3" s="18" t="str">
         <x:v>距离来源：0固定；1装备攻击范围加值。</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="3" t="n">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="n">
+      <x:c r="B4" s="14" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="n">
+      <x:c r="C4" s="14" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="n">
+      <x:c r="D4" s="19" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="n">
+      <x:c r="E4" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="3" t="n">
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="n">
+      <x:c r="B5" s="14" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="n">
+      <x:c r="C5" s="14" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="n">
+      <x:c r="D5" s="19" t="n">
         <x:v>2.1</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="n">
+      <x:c r="E5" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="3" t="n">
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="n">
+      <x:c r="B6" s="14" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="n">
+      <x:c r="C6" s="14" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="n">
+      <x:c r="D6" s="19" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="n">
+      <x:c r="E6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D7" s="19" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgCombatSkills.xlsx
+++ b/config/excel/CfgCombatSkills.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatSkills" sheetId="1" r:id="Rde11d8c89507431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatSkills" sheetId="1" r:id="R31f441d5a10e414d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -529,6 +529,40 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
